--- a/hrcheck/examples/mini_test2/本月花名册_修复建议_已确认.xlsx
+++ b/hrcheck/examples/mini_test2/本月花名册_修复建议_已确认.xlsx
@@ -716,7 +716,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>张三副本</t>
+          <t>张三2号</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -933,11 +933,7 @@
           <t>字段 直属上级工号 需要补充信息</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
@@ -1004,11 +1000,7 @@
           <t>字段 直属上级工号 需要补充信息</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
@@ -1075,11 +1067,7 @@
           <t>字段 直属上级工号 需要补充信息</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
@@ -1146,11 +1134,7 @@
           <t>字段 直属上级工号 需要补充信息</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
